--- a/output/pdf_financials_xlsx/NICN.xlsx
+++ b/output/pdf_financials_xlsx/NICN.xlsx
@@ -2474,19 +2474,19 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.199764</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.356496</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.259964</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.5550659999999999</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.599249</v>
       </c>
     </row>
     <row r="93">
@@ -3942,7 +3942,11 @@
           <t>Share-based payments reserve 7</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -4330,7 +4334,11 @@
           <t>Share-based payments reserve 8</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" s="5" t="n">
         <v>0.199764</v>
       </c>

--- a/output/pdf_financials_xlsx/NICN.xlsx
+++ b/output/pdf_financials_xlsx/NICN.xlsx
@@ -669,19 +669,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001343</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.090432</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.117019</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.047508</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.015431</v>
       </c>
     </row>
     <row r="13">
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.275202</v>
+        <v>-1.273859</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-3.803374</v>
+        <v>-3.712942</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.570084</v>
+        <v>-3.687103</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.409375</v>
+        <v>-1.456883</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.734675</v>
+        <v>-1.750106</v>
       </c>
     </row>
     <row r="28">
@@ -1063,19 +1063,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.275202</v>
+        <v>-1.273859</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-3.803374</v>
+        <v>-3.712942</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.570084</v>
+        <v>-3.687103</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.409375</v>
+        <v>-1.456883</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.734675</v>
+        <v>-1.750106</v>
       </c>
     </row>
     <row r="30">
@@ -1187,10 +1187,10 @@
         <v>1.148919</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.9744930000000001</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.190486</v>
       </c>
     </row>
     <row r="35">
@@ -1231,10 +1231,10 @@
         <v>1.148919</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.9744930000000001</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.190486</v>
       </c>
     </row>
     <row r="37">
@@ -1495,10 +1495,10 @@
         <v>0.059275</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.00832</v>
+        <v>0.033827</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.246121</v>
+        <v>0.055635</v>
       </c>
     </row>
     <row r="49">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -8748,7 +8748,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -9253,7 +9253,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E144" s="5" t="n">

--- a/output/pdf_financials_xlsx/NICN.xlsx
+++ b/output/pdf_financials_xlsx/NICN.xlsx
@@ -559,19 +559,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.132125</v>
+        <v>0.167375</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.50651</v>
+        <v>0.684203</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.532604</v>
+        <v>0.737266</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.598309</v>
+        <v>0.802444</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.424564</v>
+        <v>0.552438</v>
       </c>
     </row>
     <row r="8">
@@ -8479,7 +8479,11 @@
           <t>Director fees 9</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -9095,7 +9099,11 @@
           <t>Director fees 10</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E140" s="5" t="n">
         <v>0.03525</v>
       </c>
